--- a/data/All lungs and brain_cleaned_Dec2025_NK.xlsx
+++ b/data/All lungs and brain_cleaned_Dec2025_NK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/marius_botos_unibe_ch/Documents/Nedim/2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{4620E14E-0D55-4406-876F-ACDAAD386DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{463FB91C-C4F1-4A39-8D72-E657164EC4B2}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{4620E14E-0D55-4406-876F-ACDAAD386DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{892251C6-FC3A-4F89-B2A7-7D11B5DD3C37}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-10690" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="5" xr2:uid="{DCCBD89E-2D43-412B-9691-7E9CC62F784F}"/>
+    <workbookView minimized="1" xWindow="12240" yWindow="630" windowWidth="24345" windowHeight="15570" firstSheet="1" activeTab="1" xr2:uid="{DCCBD89E-2D43-412B-9691-7E9CC62F784F}"/>
   </bookViews>
   <sheets>
     <sheet name="478 lungs" sheetId="1" r:id="rId1"/>
@@ -4605,27 +4605,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA296"/>
-  <sheetFormatPr defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.3984375" customWidth="1"/>
-    <col min="2" max="2" width="24.265625" customWidth="1"/>
-    <col min="3" max="3" width="22.59765625" style="285" customWidth="1"/>
-    <col min="4" max="4" width="9.265625" customWidth="1"/>
-    <col min="5" max="5" width="6.86328125" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="285" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="5.86328125" customWidth="1"/>
-    <col min="8" max="8" width="3.86328125" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" customWidth="1"/>
     <col min="9" max="9" width="4" customWidth="1"/>
-    <col min="10" max="10" width="4.265625" customWidth="1"/>
-    <col min="11" max="11" width="8.3984375" style="286" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" style="286" customWidth="1"/>
     <col min="12" max="12" width="18" style="288" customWidth="1"/>
-    <col min="13" max="17" width="11.3984375" style="288"/>
-    <col min="18" max="20" width="13.1328125" style="288" customWidth="1"/>
-    <col min="21" max="21" width="11.3984375" style="291"/>
-    <col min="23" max="23" width="16.1328125" customWidth="1"/>
+    <col min="13" max="17" width="11.42578125" style="288"/>
+    <col min="18" max="20" width="13.140625" style="288" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" style="291"/>
+    <col min="23" max="23" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="61.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="283" t="s">
         <v>0</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>85</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>86</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>87</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>88</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>90</v>
       </c>
@@ -7090,7 +7090,7 @@
       <c r="Z36" s="302"/>
       <c r="AA36" s="302"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>93</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -7446,7 +7446,7 @@
       <c r="Z41" s="302"/>
       <c r="AA41" s="302"/>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>99</v>
       </c>
@@ -7517,7 +7517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>101</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>106</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>108</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>109</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>113</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>115</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>119</v>
       </c>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="X58" s="302"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>120</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>122</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>125</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>127</v>
       </c>
@@ -9151,7 +9151,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>128</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>129</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>130</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>134</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>135</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>137</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>138</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>140</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>142</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>143</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>145</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>146</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>148</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>149</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>150</v>
       </c>
@@ -10208,7 +10208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>151</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>152</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>153</v>
       </c>
@@ -10412,7 +10412,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>154</v>
       </c>
@@ -10480,7 +10480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>155</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>156</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>157</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>158</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>159</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>160</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>161</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>162</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>163</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>164</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>165</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>166</v>
       </c>
@@ -11296,7 +11296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>167</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>168</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>169</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>170</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>171</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>172</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>173</v>
       </c>
@@ -11772,7 +11772,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>174</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>175</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>177</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>178</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>179</v>
       </c>
@@ -12106,7 +12106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>180</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>181</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>182</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>183</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>184</v>
       </c>
@@ -12431,7 +12431,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>186</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>187</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>188</v>
       </c>
@@ -12626,7 +12626,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>189</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>190</v>
       </c>
@@ -12756,7 +12756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>191</v>
       </c>
@@ -12821,7 +12821,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>192</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>193</v>
       </c>
@@ -12951,7 +12951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>194</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>195</v>
       </c>
@@ -13081,7 +13081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>196</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>197</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>198</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>199</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>200</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>201</v>
       </c>
@@ -13459,7 +13459,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>202</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>203</v>
       </c>
@@ -13589,7 +13589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>204</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>206</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>207</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>208</v>
       </c>
@@ -13849,7 +13849,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>209</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>210</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>211</v>
       </c>
@@ -14044,7 +14044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>212</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>213</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>214</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>215</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>216</v>
       </c>
@@ -14369,7 +14369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>217</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>218</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>219</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>220</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>221</v>
       </c>
@@ -14694,7 +14694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>222</v>
       </c>
@@ -14759,7 +14759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>223</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>224</v>
       </c>
@@ -14889,7 +14889,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>225</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>226</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>227</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>228</v>
       </c>
@@ -15149,7 +15149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>229</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>230</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>231</v>
       </c>
@@ -15344,7 +15344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>232</v>
       </c>
@@ -15409,7 +15409,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>233</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>234</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>235</v>
       </c>
@@ -15604,7 +15604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>236</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>237</v>
       </c>
@@ -15734,7 +15734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>238</v>
       </c>
@@ -15799,7 +15799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>239</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>240</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>241</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>242</v>
       </c>
@@ -16059,7 +16059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>244</v>
       </c>
@@ -16124,7 +16124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>245</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>246</v>
       </c>
@@ -16254,7 +16254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>247</v>
       </c>
@@ -16319,7 +16319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>248</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>249</v>
       </c>
@@ -16449,7 +16449,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>250</v>
       </c>
@@ -16514,7 +16514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>251</v>
       </c>
@@ -16579,7 +16579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>252</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>253</v>
       </c>
@@ -16709,7 +16709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>254</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>255</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>256</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>257</v>
       </c>
@@ -16969,7 +16969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>258</v>
       </c>
@@ -17031,7 +17031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>259</v>
       </c>
@@ -17096,7 +17096,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>261</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>262</v>
       </c>
@@ -17226,7 +17226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>263</v>
       </c>
@@ -17291,7 +17291,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>264</v>
       </c>
@@ -17356,7 +17356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>265</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>266</v>
       </c>
@@ -17486,7 +17486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>267</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>268</v>
       </c>
@@ -17616,7 +17616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>270</v>
       </c>
@@ -17681,7 +17681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>271</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>272</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>273</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>276</v>
       </c>
@@ -17941,7 +17941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>277</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>278</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>280</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>281</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>282</v>
       </c>
@@ -18206,7 +18206,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>283</v>
       </c>
@@ -18256,7 +18256,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>284</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>286</v>
       </c>
@@ -18386,7 +18386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>287</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>288</v>
       </c>
@@ -18516,7 +18516,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>289</v>
       </c>
@@ -18581,7 +18581,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>290</v>
       </c>
@@ -18646,7 +18646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>291</v>
       </c>
@@ -18711,7 +18711,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>292</v>
       </c>
@@ -18776,7 +18776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>293</v>
       </c>
@@ -18841,7 +18841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>294</v>
       </c>
@@ -18906,7 +18906,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>295</v>
       </c>
@@ -18971,7 +18971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>296</v>
       </c>
@@ -19036,7 +19036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>297</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>298</v>
       </c>
@@ -19166,7 +19166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>299</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>300</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>301</v>
       </c>
@@ -19361,7 +19361,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>302</v>
       </c>
@@ -19426,7 +19426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>303</v>
       </c>
@@ -19491,7 +19491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>304</v>
       </c>
@@ -19556,7 +19556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>305</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>308</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>309</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>310</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>313</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>314</v>
       </c>
@@ -19934,7 +19934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>315</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>316</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>317</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>318</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>319</v>
       </c>
@@ -20244,7 +20244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>321</v>
       </c>
@@ -20297,7 +20297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>322</v>
       </c>
@@ -20350,7 +20350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" s="289" t="s">
         <v>323</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" s="289" t="s">
         <v>325</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" s="289" t="s">
         <v>326</v>
       </c>
@@ -20469,7 +20469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" s="289" t="s">
         <v>327</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" s="289" t="s">
         <v>328</v>
       </c>
@@ -20547,7 +20547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" s="289" t="s">
         <v>329</v>
       </c>
@@ -20586,7 +20586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" s="289" t="s">
         <v>330</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" s="289" t="s">
         <v>331</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" s="289" t="s">
         <v>332</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="289" t="s">
         <v>333</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="289" t="s">
         <v>334</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="289" t="s">
         <v>335</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>336</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>339</v>
       </c>
@@ -20930,7 +20930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>340</v>
       </c>
@@ -20998,7 +20998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>341</v>
       </c>
@@ -21066,7 +21066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>342</v>
       </c>
@@ -21134,7 +21134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>343</v>
       </c>
@@ -21202,7 +21202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>344</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>345</v>
       </c>
@@ -21338,7 +21338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>346</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>347</v>
       </c>
@@ -21474,7 +21474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>348</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>350</v>
       </c>
@@ -21610,7 +21610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>351</v>
       </c>
@@ -21678,7 +21678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>352</v>
       </c>
@@ -21746,7 +21746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>353</v>
       </c>
@@ -21814,7 +21814,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>354</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>355</v>
       </c>
@@ -21950,7 +21950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>356</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>357</v>
       </c>
@@ -22073,7 +22073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
         <v>359</v>
       </c>
@@ -22128,7 +22128,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>360</v>
       </c>
@@ -22196,7 +22196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>361</v>
       </c>
@@ -22264,7 +22264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>362</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>363</v>
       </c>
@@ -22400,7 +22400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>364</v>
       </c>
@@ -22468,7 +22468,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>365</v>
       </c>
@@ -22536,7 +22536,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>366</v>
       </c>
@@ -22591,7 +22591,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>367</v>
       </c>
@@ -22646,7 +22646,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>368</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>371</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>372</v>
       </c>
@@ -22850,7 +22850,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>373</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>374</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>375</v>
       </c>
@@ -23054,7 +23054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>376</v>
       </c>
@@ -23122,7 +23122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>377</v>
       </c>
@@ -23190,7 +23190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>378</v>
       </c>
@@ -23258,7 +23258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>379</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" s="3"/>
       <c r="B290" s="3" t="s">
         <v>369</v>
@@ -23384,7 +23384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>381</v>
       </c>
@@ -23447,7 +23447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:23" x14ac:dyDescent="0.25">
       <c r="L295" s="288">
         <v>33</v>
       </c>
@@ -23479,7 +23479,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
       <c r="M296" s="340"/>
       <c r="N296" s="340"/>
       <c r="O296" s="340"/>
@@ -23503,31 +23503,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD254CE-78CF-43A3-800A-36636E7DA7F7}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA249"/>
-  <sheetFormatPr defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="285" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.3984375" style="286" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.86328125" style="288" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="286" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="288" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="11" style="288" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="12.3984375" style="288" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="12.42578125" style="288" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" style="288" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.1328125" style="288" customWidth="1"/>
-    <col min="20" max="20" width="12.3984375" style="288" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.265625" style="291" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="288" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" style="288" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.28515625" style="291" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="61.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="283" t="s">
         <v>0</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -23740,7 +23740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -23811,7 +23811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -23882,7 +23882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -23953,7 +23953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -24087,7 +24087,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -24158,7 +24158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -24300,7 +24300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -24371,7 +24371,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -24439,7 +24439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -24510,7 +24510,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -24652,7 +24652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -24723,7 +24723,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -24794,7 +24794,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -24865,7 +24865,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -24936,7 +24936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -25007,7 +25007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -25149,7 +25149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -25220,7 +25220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -25362,7 +25362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -25433,7 +25433,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -25504,7 +25504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -25575,7 +25575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>85</v>
       </c>
@@ -25646,7 +25646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -25717,7 +25717,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -25788,7 +25788,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -25859,7 +25859,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -25934,7 +25934,7 @@
       <c r="Z34" s="302"/>
       <c r="AA34" s="302"/>
     </row>
-    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>92</v>
       </c>
@@ -26005,7 +26005,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -26076,7 +26076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -26147,7 +26147,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -26215,7 +26215,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>97</v>
       </c>
@@ -26290,7 +26290,7 @@
       <c r="Z39" s="302"/>
       <c r="AA39" s="302"/>
     </row>
-    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -26361,7 +26361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -26432,7 +26432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>102</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -26574,7 +26574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -26645,7 +26645,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>106</v>
       </c>
@@ -26716,7 +26716,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>107</v>
       </c>
@@ -26787,7 +26787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -26855,7 +26855,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>111</v>
       </c>
@@ -26926,7 +26926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>113</v>
       </c>
@@ -26997,7 +26997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -27068,7 +27068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>115</v>
       </c>
@@ -27139,7 +27139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -27210,7 +27210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -27281,7 +27281,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -27350,7 +27350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -27420,7 +27420,7 @@
       </c>
       <c r="X55" s="302"/>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>120</v>
       </c>
@@ -27491,7 +27491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>121</v>
       </c>
@@ -27562,7 +27562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -27633,7 +27633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>123</v>
       </c>
@@ -27704,7 +27704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>124</v>
       </c>
@@ -27775,7 +27775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>125</v>
       </c>
@@ -27846,7 +27846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>126</v>
       </c>
@@ -27917,7 +27917,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>132</v>
       </c>
@@ -28059,7 +28059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -28130,7 +28130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>135</v>
       </c>
@@ -28201,7 +28201,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>137</v>
       </c>
@@ -28272,7 +28272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>138</v>
       </c>
@@ -28343,7 +28343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>140</v>
       </c>
@@ -28414,7 +28414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>142</v>
       </c>
@@ -28485,7 +28485,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -28556,7 +28556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>145</v>
       </c>
@@ -28627,7 +28627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>146</v>
       </c>
@@ -28698,7 +28698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>148</v>
       </c>
@@ -28769,7 +28769,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -28840,7 +28840,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -28911,7 +28911,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>151</v>
       </c>
@@ -28982,7 +28982,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -29053,7 +29053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>153</v>
       </c>
@@ -29124,7 +29124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -29195,7 +29195,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -29266,7 +29266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>156</v>
       </c>
@@ -29337,7 +29337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>157</v>
       </c>
@@ -29408,7 +29408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>158</v>
       </c>
@@ -29479,7 +29479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>159</v>
       </c>
@@ -29550,7 +29550,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>160</v>
       </c>
@@ -29621,7 +29621,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>161</v>
       </c>
@@ -29692,7 +29692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>162</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>163</v>
       </c>
@@ -29834,7 +29834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>164</v>
       </c>
@@ -29905,7 +29905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>165</v>
       </c>
@@ -29976,7 +29976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>166</v>
       </c>
@@ -30047,7 +30047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>167</v>
       </c>
@@ -30118,7 +30118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>168</v>
       </c>
@@ -30189,7 +30189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>169</v>
       </c>
@@ -30260,7 +30260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>170</v>
       </c>
@@ -30331,7 +30331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>171</v>
       </c>
@@ -30402,7 +30402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>172</v>
       </c>
@@ -30473,7 +30473,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>173</v>
       </c>
@@ -30544,7 +30544,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>174</v>
       </c>
@@ -30615,7 +30615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>175</v>
       </c>
@@ -30686,7 +30686,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>177</v>
       </c>
@@ -30757,7 +30757,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>178</v>
       </c>
@@ -30825,7 +30825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>179</v>
       </c>
@@ -30893,7 +30893,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>180</v>
       </c>
@@ -30961,7 +30961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>181</v>
       </c>
@@ -31029,7 +31029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>182</v>
       </c>
@@ -31097,7 +31097,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>183</v>
       </c>
@@ -31165,7 +31165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>184</v>
       </c>
@@ -31233,7 +31233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>186</v>
       </c>
@@ -31301,7 +31301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -31369,7 +31369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>188</v>
       </c>
@@ -31437,7 +31437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>189</v>
       </c>
@@ -31505,7 +31505,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>190</v>
       </c>
@@ -31573,7 +31573,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>191</v>
       </c>
@@ -31641,7 +31641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>192</v>
       </c>
@@ -31709,7 +31709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>193</v>
       </c>
@@ -31777,7 +31777,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>194</v>
       </c>
@@ -31845,7 +31845,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>195</v>
       </c>
@@ -31913,7 +31913,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>196</v>
       </c>
@@ -31981,7 +31981,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>197</v>
       </c>
@@ -32049,7 +32049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>198</v>
       </c>
@@ -32117,7 +32117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>199</v>
       </c>
@@ -32185,7 +32185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>201</v>
       </c>
@@ -32253,7 +32253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>202</v>
       </c>
@@ -32321,7 +32321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>203</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>204</v>
       </c>
@@ -32457,7 +32457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>206</v>
       </c>
@@ -32525,7 +32525,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>207</v>
       </c>
@@ -32593,7 +32593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>208</v>
       </c>
@@ -32661,7 +32661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>209</v>
       </c>
@@ -32729,7 +32729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>210</v>
       </c>
@@ -32797,7 +32797,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>211</v>
       </c>
@@ -32865,7 +32865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>212</v>
       </c>
@@ -32933,7 +32933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>213</v>
       </c>
@@ -33001,7 +33001,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>214</v>
       </c>
@@ -33069,7 +33069,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>215</v>
       </c>
@@ -33137,7 +33137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>216</v>
       </c>
@@ -33205,7 +33205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>217</v>
       </c>
@@ -33273,7 +33273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>218</v>
       </c>
@@ -33341,7 +33341,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>219</v>
       </c>
@@ -33409,7 +33409,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>220</v>
       </c>
@@ -33477,7 +33477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>221</v>
       </c>
@@ -33545,7 +33545,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>222</v>
       </c>
@@ -33613,7 +33613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>223</v>
       </c>
@@ -33681,7 +33681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>224</v>
       </c>
@@ -33749,7 +33749,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>225</v>
       </c>
@@ -33817,7 +33817,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>226</v>
       </c>
@@ -33885,7 +33885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>227</v>
       </c>
@@ -33953,7 +33953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>228</v>
       </c>
@@ -34021,7 +34021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>229</v>
       </c>
@@ -34089,7 +34089,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>230</v>
       </c>
@@ -34157,7 +34157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>231</v>
       </c>
@@ -34225,7 +34225,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>232</v>
       </c>
@@ -34293,7 +34293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>233</v>
       </c>
@@ -34361,7 +34361,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>234</v>
       </c>
@@ -34429,7 +34429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>235</v>
       </c>
@@ -34497,7 +34497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>236</v>
       </c>
@@ -34565,7 +34565,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>237</v>
       </c>
@@ -34633,7 +34633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>238</v>
       </c>
@@ -34701,7 +34701,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>239</v>
       </c>
@@ -34769,7 +34769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>240</v>
       </c>
@@ -34837,7 +34837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>241</v>
       </c>
@@ -34905,7 +34905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>242</v>
       </c>
@@ -34973,7 +34973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>244</v>
       </c>
@@ -35041,7 +35041,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>245</v>
       </c>
@@ -35109,7 +35109,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>246</v>
       </c>
@@ -35177,7 +35177,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>247</v>
       </c>
@@ -35245,7 +35245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>248</v>
       </c>
@@ -35313,7 +35313,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>249</v>
       </c>
@@ -35381,7 +35381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>250</v>
       </c>
@@ -35449,7 +35449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>251</v>
       </c>
@@ -35517,7 +35517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>252</v>
       </c>
@@ -35585,7 +35585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>253</v>
       </c>
@@ -35653,7 +35653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>254</v>
       </c>
@@ -35721,7 +35721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>255</v>
       </c>
@@ -35789,7 +35789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -35857,7 +35857,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>257</v>
       </c>
@@ -35925,7 +35925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>258</v>
       </c>
@@ -35990,7 +35990,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>259</v>
       </c>
@@ -36058,7 +36058,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>261</v>
       </c>
@@ -36126,7 +36126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>262</v>
       </c>
@@ -36194,7 +36194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>263</v>
       </c>
@@ -36262,7 +36262,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>264</v>
       </c>
@@ -36330,7 +36330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>265</v>
       </c>
@@ -36398,7 +36398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>266</v>
       </c>
@@ -36466,7 +36466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>267</v>
       </c>
@@ -36534,7 +36534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>268</v>
       </c>
@@ -36602,7 +36602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>270</v>
       </c>
@@ -36670,7 +36670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>271</v>
       </c>
@@ -36738,7 +36738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>272</v>
       </c>
@@ -36806,7 +36806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>273</v>
       </c>
@@ -36874,7 +36874,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>276</v>
       </c>
@@ -36942,7 +36942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>277</v>
       </c>
@@ -37010,7 +37010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>284</v>
       </c>
@@ -37078,7 +37078,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>286</v>
       </c>
@@ -37146,7 +37146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>287</v>
       </c>
@@ -37214,7 +37214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>288</v>
       </c>
@@ -37282,7 +37282,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>289</v>
       </c>
@@ -37350,7 +37350,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>290</v>
       </c>
@@ -37418,7 +37418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>291</v>
       </c>
@@ -37486,7 +37486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>292</v>
       </c>
@@ -37554,7 +37554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>293</v>
       </c>
@@ -37622,7 +37622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="204" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>294</v>
       </c>
@@ -37690,7 +37690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>295</v>
       </c>
@@ -37758,7 +37758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>296</v>
       </c>
@@ -37826,7 +37826,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>297</v>
       </c>
@@ -37894,7 +37894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>298</v>
       </c>
@@ -37962,7 +37962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>299</v>
       </c>
@@ -38030,7 +38030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>300</v>
       </c>
@@ -38098,7 +38098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>301</v>
       </c>
@@ -38166,7 +38166,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="212" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>302</v>
       </c>
@@ -38234,7 +38234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>303</v>
       </c>
@@ -38302,7 +38302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>304</v>
       </c>
@@ -38370,7 +38370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>309</v>
       </c>
@@ -38438,7 +38438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>360</v>
       </c>
@@ -38509,7 +38509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>361</v>
       </c>
@@ -38580,7 +38580,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="218" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>362</v>
       </c>
@@ -38651,7 +38651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>363</v>
       </c>
@@ -38722,7 +38722,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>364</v>
       </c>
@@ -38793,7 +38793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>365</v>
       </c>
@@ -38864,7 +38864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>368</v>
       </c>
@@ -38935,7 +38935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>371</v>
       </c>
@@ -39006,7 +39006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>372</v>
       </c>
@@ -39077,7 +39077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>373</v>
       </c>
@@ -39148,7 +39148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>374</v>
       </c>
@@ -39219,7 +39219,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>375</v>
       </c>
@@ -39290,7 +39290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>376</v>
       </c>
@@ -39361,7 +39361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="229" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>377</v>
       </c>
@@ -39432,7 +39432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>378</v>
       </c>
@@ -39503,7 +39503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>379</v>
       </c>
@@ -39571,7 +39571,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>387</v>
       </c>
@@ -39637,7 +39637,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>381</v>
       </c>
@@ -39703,7 +39703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>340</v>
       </c>
@@ -39774,7 +39774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>341</v>
       </c>
@@ -39845,7 +39845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>342</v>
       </c>
@@ -39916,7 +39916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>343</v>
       </c>
@@ -39987,7 +39987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>344</v>
       </c>
@@ -40058,7 +40058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>345</v>
       </c>
@@ -40129,7 +40129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>346</v>
       </c>
@@ -40200,7 +40200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>347</v>
       </c>
@@ -40271,7 +40271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>348</v>
       </c>
@@ -40342,7 +40342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>350</v>
       </c>
@@ -40413,7 +40413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>351</v>
       </c>
@@ -40484,7 +40484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>352</v>
       </c>
@@ -40555,7 +40555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>353</v>
       </c>
@@ -40626,7 +40626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>354</v>
       </c>
@@ -40697,7 +40697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>355</v>
       </c>
@@ -40768,7 +40768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>356</v>
       </c>
@@ -40840,13 +40840,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA249" xr:uid="{FCD254CE-78CF-43A3-800A-36636E7DA7F7}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="63.27496381"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AA249" xr:uid="{FCD254CE-78CF-43A3-800A-36636E7DA7F7}"/>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -40859,13 +40853,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B0E25A-DE30-411F-8E4F-A1D55CA9CF94}">
   <dimension ref="A1:AD23"/>
-  <sheetFormatPr defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="12" max="12" width="23.1328125" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>388</v>
       </c>
@@ -40901,7 +40895,7 @@
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
     </row>
-    <row r="2" spans="1:30" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -40993,7 +40987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -41055,7 +41049,7 @@
         <v>0.98571312820810197</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -41147,7 +41141,7 @@
         <v>2.42628322839364E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>395</v>
       </c>
@@ -41209,7 +41203,7 @@
         <v>0.10337044943015999</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -41271,7 +41265,7 @@
         <v>5.2409940654489498E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>396</v>
       </c>
@@ -41333,7 +41327,7 @@
         <v>0.68761575497650496</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>397</v>
       </c>
@@ -41395,7 +41389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -41457,7 +41451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -41519,7 +41513,7 @@
         <v>1.8034902158240999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -41581,7 +41575,7 @@
         <v>0.18267269251704299</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -41643,7 +41637,7 @@
         <v>7.3782459623707001E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -41705,7 +41699,7 @@
         <v>38.356126209693898</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -41767,7 +41761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="26:26" x14ac:dyDescent="0.45">
+    <row r="23" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z23" s="279"/>
     </row>
   </sheetData>
@@ -41779,27 +41773,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA7EA51-F1D2-4953-AEA3-99CD75339BE8}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AG136"/>
-  <sheetFormatPr defaultColWidth="10.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.73046875" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" customWidth="1"/>
-    <col min="7" max="7" width="16.1328125" customWidth="1"/>
-    <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.1328125" customWidth="1"/>
-    <col min="12" max="12" width="19.1328125" customWidth="1"/>
-    <col min="13" max="13" width="16.86328125" customWidth="1"/>
-    <col min="14" max="14" width="12.1328125" customWidth="1"/>
-    <col min="15" max="15" width="17.3984375" customWidth="1"/>
-    <col min="20" max="20" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3984375" customWidth="1"/>
-    <col min="24" max="24" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.3984375" customWidth="1"/>
-    <col min="33" max="33" width="8.86328125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.42578125" customWidth="1"/>
+    <col min="33" max="33" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="78.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" ht="81" x14ac:dyDescent="0.25">
       <c r="A1" s="271" t="s">
         <v>1</v>
       </c>
@@ -41900,7 +41894,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="281" t="s">
         <v>133</v>
       </c>
@@ -41998,7 +41992,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
         <v>133</v>
       </c>
@@ -42114,7 +42108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>133</v>
       </c>
@@ -42210,7 +42204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:33" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
         <v>133</v>
       </c>
@@ -42308,7 +42302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:33" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>133</v>
       </c>
@@ -42424,7 +42418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:33" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>133</v>
       </c>
@@ -42540,7 +42534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>133</v>
       </c>
@@ -42638,7 +42632,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>133</v>
       </c>
@@ -42754,7 +42748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58" t="s">
         <v>133</v>
       </c>
@@ -42852,7 +42846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="78" t="s">
         <v>147</v>
       </c>
@@ -42968,7 +42962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>147</v>
       </c>
@@ -43066,7 +43060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>147</v>
       </c>
@@ -43180,7 +43174,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>147</v>
       </c>
@@ -43278,7 +43272,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>147</v>
       </c>
@@ -43392,7 +43386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>147</v>
       </c>
@@ -43506,7 +43500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>147</v>
       </c>
@@ -43602,7 +43596,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>147</v>
       </c>
@@ -43716,7 +43710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
         <v>147</v>
       </c>
@@ -43814,7 +43808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
         <v>147</v>
       </c>
@@ -43930,7 +43924,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>147</v>
       </c>
@@ -44046,7 +44040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>147</v>
       </c>
@@ -44162,7 +44156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="103" t="s">
         <v>147</v>
       </c>
@@ -44276,7 +44270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:33" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>58</v>
       </c>
@@ -44392,7 +44386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>58</v>
       </c>
@@ -44508,7 +44502,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
         <v>58</v>
       </c>
@@ -44624,7 +44618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>58</v>
       </c>
@@ -44720,7 +44714,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
         <v>58</v>
       </c>
@@ -44816,7 +44810,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="28.9" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:33" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="58" t="s">
         <v>58</v>
       </c>
@@ -44914,7 +44908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A30" s="78" t="s">
         <v>91</v>
       </c>
@@ -45030,7 +45024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
         <v>91</v>
       </c>
@@ -45146,7 +45140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>91</v>
       </c>
@@ -45262,7 +45256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
         <v>91</v>
       </c>
@@ -45376,7 +45370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="103" t="s">
         <v>91</v>
       </c>
@@ -45472,7 +45466,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>69</v>
       </c>
@@ -45586,7 +45580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="58" t="s">
         <v>69</v>
       </c>
@@ -45700,7 +45694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="28.9" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:33" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78" t="s">
         <v>72</v>
       </c>
@@ -45798,7 +45792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="103" t="s">
         <v>72</v>
       </c>
@@ -45894,7 +45888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>112</v>
       </c>
@@ -46008,7 +46002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="32" t="s">
         <v>112</v>
       </c>
@@ -46104,7 +46098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
         <v>112</v>
       </c>
@@ -46200,7 +46194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="58" t="s">
         <v>112</v>
       </c>
@@ -46296,7 +46290,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="78" t="s">
         <v>42</v>
       </c>
@@ -46410,7 +46404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="103" t="s">
         <v>42</v>
       </c>
@@ -46524,7 +46518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>176</v>
       </c>
@@ -46620,7 +46614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>176</v>
       </c>
@@ -46736,7 +46730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>176</v>
       </c>
@@ -46832,7 +46826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
         <v>176</v>
       </c>
@@ -46928,7 +46922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32" t="s">
         <v>176</v>
       </c>
@@ -47042,7 +47036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="32" t="s">
         <v>176</v>
       </c>
@@ -47138,7 +47132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="32" t="s">
         <v>176</v>
       </c>
@@ -47234,7 +47228,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="58" t="s">
         <v>176</v>
       </c>
@@ -47330,7 +47324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A53" s="78" t="s">
         <v>475</v>
       </c>
@@ -47426,7 +47420,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32" t="s">
         <v>475</v>
       </c>
@@ -47522,7 +47516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="103" t="s">
         <v>475</v>
       </c>
@@ -47620,7 +47614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="15" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:33" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="188" t="s">
         <v>479</v>
       </c>
@@ -47734,7 +47728,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A57" s="78" t="s">
         <v>311</v>
       </c>
@@ -47850,7 +47844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="32" t="s">
         <v>311</v>
       </c>
@@ -47964,7 +47958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32" t="s">
         <v>311</v>
       </c>
@@ -48078,7 +48072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="32" t="s">
         <v>311</v>
       </c>
@@ -48192,7 +48186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="32" t="s">
         <v>311</v>
       </c>
@@ -48306,7 +48300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="32" t="s">
         <v>311</v>
       </c>
@@ -48420,7 +48414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="103" t="s">
         <v>311</v>
       </c>
@@ -48534,7 +48528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>320</v>
       </c>
@@ -48648,7 +48642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
         <v>320</v>
       </c>
@@ -48762,7 +48756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="58" t="s">
         <v>320</v>
       </c>
@@ -48858,7 +48852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A67" s="78" t="s">
         <v>369</v>
       </c>
@@ -48954,7 +48948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="32" t="s">
         <v>369</v>
       </c>
@@ -49070,7 +49064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32" t="s">
         <v>369</v>
       </c>
@@ -49168,7 +49162,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
         <v>369</v>
       </c>
@@ -49264,7 +49258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
         <v>369</v>
       </c>
@@ -49378,7 +49372,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="32" t="s">
         <v>369</v>
       </c>
@@ -49474,7 +49468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="32" t="s">
         <v>369</v>
       </c>
@@ -49570,7 +49564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32" t="s">
         <v>369</v>
       </c>
@@ -49668,7 +49662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="32" t="s">
         <v>369</v>
       </c>
@@ -49766,7 +49760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="32" t="s">
         <v>369</v>
       </c>
@@ -49864,7 +49858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="32" t="s">
         <v>493</v>
       </c>
@@ -49980,7 +49974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="32" t="s">
         <v>493</v>
       </c>
@@ -50096,7 +50090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="32" t="s">
         <v>493</v>
       </c>
@@ -50192,7 +50186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="32" t="s">
         <v>493</v>
       </c>
@@ -50306,7 +50300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="32" t="s">
         <v>493</v>
       </c>
@@ -50420,7 +50414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="32" t="s">
         <v>493</v>
       </c>
@@ -50516,7 +50510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="32" t="s">
         <v>493</v>
       </c>
@@ -50612,7 +50606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32" t="s">
         <v>493</v>
       </c>
@@ -50708,7 +50702,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="32" t="s">
         <v>493</v>
       </c>
@@ -50804,7 +50798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
         <v>493</v>
       </c>
@@ -50900,7 +50894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="32" t="s">
         <v>493</v>
       </c>
@@ -50996,7 +50990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="32" t="s">
         <v>493</v>
       </c>
@@ -51092,7 +51086,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="103" t="s">
         <v>493</v>
       </c>
@@ -51188,7 +51182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
         <v>507</v>
       </c>
@@ -51304,7 +51298,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="58" t="s">
         <v>507</v>
       </c>
@@ -51420,7 +51414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="15" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:33" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="220" t="s">
         <v>77</v>
       </c>
@@ -51516,7 +51510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
         <v>80</v>
       </c>
@@ -51614,7 +51608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="32" t="s">
         <v>80</v>
       </c>
@@ -51710,7 +51704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="32" t="s">
         <v>80</v>
       </c>
@@ -51826,7 +51820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="32" t="s">
         <v>80</v>
       </c>
@@ -51940,7 +51934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="32" t="s">
         <v>80</v>
       </c>
@@ -52054,7 +52048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="58" t="s">
         <v>80</v>
       </c>
@@ -52168,7 +52162,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A99" s="78" t="s">
         <v>260</v>
       </c>
@@ -52264,7 +52258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="32" t="s">
         <v>260</v>
       </c>
@@ -52360,7 +52354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="32" t="s">
         <v>260</v>
       </c>
@@ -52456,7 +52450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="32" t="s">
         <v>260</v>
       </c>
@@ -52552,7 +52546,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="32" t="s">
         <v>260</v>
       </c>
@@ -52648,7 +52642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="32" t="s">
         <v>260</v>
       </c>
@@ -52744,7 +52738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="32" t="s">
         <v>260</v>
       </c>
@@ -52840,7 +52834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:33" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="32" t="s">
         <v>260</v>
       </c>
@@ -52956,7 +52950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="32" t="s">
         <v>260</v>
       </c>
@@ -53052,7 +53046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="32" t="s">
         <v>260</v>
       </c>
@@ -53148,7 +53142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="32" t="s">
         <v>260</v>
       </c>
@@ -53244,7 +53238,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="103" t="s">
         <v>260</v>
       </c>
@@ -53340,7 +53334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A111" s="78" t="s">
         <v>306</v>
       </c>
@@ -53436,7 +53430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="32" t="s">
         <v>306</v>
       </c>
@@ -53532,7 +53526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="103" t="s">
         <v>306</v>
       </c>
@@ -53646,7 +53640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A114" s="15" t="s">
         <v>185</v>
       </c>
@@ -53744,7 +53738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="32" t="s">
         <v>185</v>
       </c>
@@ -53840,7 +53834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:33" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="32" t="s">
         <v>185</v>
       </c>
@@ -53938,7 +53932,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="32" t="s">
         <v>185</v>
       </c>
@@ -54034,7 +54028,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="32" t="s">
         <v>185</v>
       </c>
@@ -54132,7 +54126,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="58" t="s">
         <v>185</v>
       </c>
@@ -54228,7 +54222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="14.65" hidden="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:33" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A120" s="78" t="s">
         <v>205</v>
       </c>
@@ -54342,7 +54336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="32" t="s">
         <v>205</v>
       </c>
@@ -54456,7 +54450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="32" t="s">
         <v>205</v>
       </c>
@@ -54572,7 +54566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="32" t="s">
         <v>205</v>
       </c>
@@ -54686,7 +54680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="32" t="s">
         <v>205</v>
       </c>
@@ -54800,7 +54794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="32" t="s">
         <v>205</v>
       </c>
@@ -54916,7 +54910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="32" t="s">
         <v>205</v>
       </c>
@@ -55030,7 +55024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="32" t="s">
         <v>205</v>
       </c>
@@ -55128,7 +55122,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="32" t="s">
         <v>205</v>
       </c>
@@ -55226,7 +55220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="32" t="s">
         <v>205</v>
       </c>
@@ -55322,7 +55316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="32" t="s">
         <v>205</v>
       </c>
@@ -55420,7 +55414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:33" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="32" t="s">
         <v>205</v>
       </c>
@@ -55516,7 +55510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:33" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="103" t="s">
         <v>205</v>
       </c>
@@ -55612,7 +55606,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="15" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:33" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="188" t="s">
         <v>552</v>
       </c>
@@ -55728,7 +55722,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="15" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:33" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="220" t="s">
         <v>89</v>
       </c>
@@ -55824,7 +55818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="15" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:33" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="188" t="s">
         <v>555</v>
       </c>
@@ -55940,7 +55934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AF136" s="277"/>
       <c r="AG136" s="277"/>
     </row>
@@ -55959,22 +55953,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD2BF15-2989-45AA-9120-3EB5C83B5713}">
   <dimension ref="A1:AQ136"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="17" max="17" width="10.3984375" customWidth="1"/>
-    <col min="20" max="20" width="9.86328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.86328125" customWidth="1"/>
-    <col min="24" max="24" width="11.265625" customWidth="1"/>
-    <col min="27" max="28" width="9.59765625" customWidth="1"/>
-    <col min="43" max="43" width="10.86328125"/>
+    <col min="17" max="17" width="10.42578125" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" customWidth="1"/>
+    <col min="27" max="28" width="9.5703125" customWidth="1"/>
+    <col min="43" max="43" width="10.85546875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="85.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:43" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -56103,7 +56097,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>132</v>
       </c>
@@ -56233,7 +56227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
         <v>134</v>
       </c>
@@ -56364,7 +56358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>135</v>
       </c>
@@ -56495,7 +56489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
         <v>137</v>
       </c>
@@ -56625,7 +56619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>138</v>
       </c>
@@ -56756,7 +56750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>140</v>
       </c>
@@ -56887,7 +56881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>142</v>
       </c>
@@ -57016,7 +57010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>143</v>
       </c>
@@ -57147,7 +57141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58" t="s">
         <v>145</v>
       </c>
@@ -57277,7 +57271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="78" t="s">
         <v>433</v>
       </c>
@@ -57410,7 +57404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>434</v>
       </c>
@@ -57544,7 +57538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>435</v>
       </c>
@@ -57661,7 +57655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>436</v>
       </c>
@@ -57795,7 +57789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>437</v>
       </c>
@@ -57918,7 +57912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>438</v>
       </c>
@@ -58039,7 +58033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>439</v>
       </c>
@@ -58173,7 +58167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>440</v>
       </c>
@@ -58288,7 +58282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
         <v>441</v>
       </c>
@@ -58422,7 +58416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
         <v>442</v>
       </c>
@@ -58537,7 +58531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>444</v>
       </c>
@@ -58663,7 +58657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>445</v>
       </c>
@@ -58784,7 +58778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="103" t="s">
         <v>446</v>
       </c>
@@ -58920,7 +58914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>57</v>
       </c>
@@ -59053,7 +59047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>447</v>
       </c>
@@ -59180,7 +59174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
         <v>449</v>
       </c>
@@ -59307,7 +59301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>62</v>
       </c>
@@ -59442,7 +59436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
         <v>63</v>
       </c>
@@ -59576,7 +59570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="58" t="s">
         <v>64</v>
       </c>
@@ -59712,7 +59706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A30" s="78" t="s">
         <v>451</v>
       </c>
@@ -59848,7 +59842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
         <v>452</v>
       </c>
@@ -59984,7 +59978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>453</v>
       </c>
@@ -60118,7 +60112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
         <v>454</v>
       </c>
@@ -60254,7 +60248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="303" t="s">
         <v>455</v>
       </c>
@@ -60377,7 +60371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="327" t="s">
         <v>456</v>
       </c>
@@ -60478,7 +60472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="315" t="s">
         <v>457</v>
       </c>
@@ -60577,7 +60571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78" t="s">
         <v>458</v>
       </c>
@@ -60711,7 +60705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="103" t="s">
         <v>460</v>
       </c>
@@ -60845,7 +60839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>461</v>
       </c>
@@ -60976,7 +60970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
         <v>462</v>
       </c>
@@ -61106,7 +61100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
         <v>463</v>
       </c>
@@ -61236,7 +61230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:43" s="3" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="315" t="s">
         <v>464</v>
       </c>
@@ -61353,7 +61347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="78" t="s">
         <v>465</v>
       </c>
@@ -61474,7 +61468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="103" t="s">
         <v>466</v>
       </c>
@@ -61593,7 +61587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>467</v>
       </c>
@@ -61726,7 +61720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>468</v>
       </c>
@@ -61862,7 +61856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>469</v>
       </c>
@@ -61993,7 +61987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>470</v>
       </c>
@@ -62127,7 +62121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32" t="s">
         <v>471</v>
       </c>
@@ -62251,7 +62245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="32" t="s">
         <v>472</v>
       </c>
@@ -62382,7 +62376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
         <v>473</v>
       </c>
@@ -62516,7 +62510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="58" t="s">
         <v>474</v>
       </c>
@@ -62647,7 +62641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A53" s="78" t="s">
         <v>476</v>
       </c>
@@ -62778,7 +62772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32" t="s">
         <v>477</v>
       </c>
@@ -62909,7 +62903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="103" t="s">
         <v>478</v>
       </c>
@@ -63044,7 +63038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="188" t="s">
         <v>480</v>
       </c>
@@ -63169,7 +63163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A57" s="78" t="s">
         <v>310</v>
       </c>
@@ -63302,7 +63296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="32" t="s">
         <v>313</v>
       </c>
@@ -63433,7 +63427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A59" s="32" t="s">
         <v>314</v>
       </c>
@@ -63564,7 +63558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="32" t="s">
         <v>315</v>
       </c>
@@ -63695,7 +63689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>316</v>
       </c>
@@ -63826,7 +63820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A62" s="32" t="s">
         <v>317</v>
       </c>
@@ -63957,7 +63951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="103" t="s">
         <v>318</v>
       </c>
@@ -64083,7 +64077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>481</v>
       </c>
@@ -64204,7 +64198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
         <v>319</v>
       </c>
@@ -64323,7 +64317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="58" t="s">
         <v>321</v>
       </c>
@@ -64450,7 +64444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A67" s="78" t="s">
         <v>482</v>
       </c>
@@ -64550,7 +64544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="32" t="s">
         <v>483</v>
       </c>
@@ -64648,7 +64642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32" t="s">
         <v>484</v>
       </c>
@@ -64746,7 +64740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
         <v>486</v>
       </c>
@@ -64844,7 +64838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
         <v>487</v>
       </c>
@@ -64942,7 +64936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="32" t="s">
         <v>488</v>
       </c>
@@ -65040,7 +65034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A73" s="32" t="s">
         <v>489</v>
       </c>
@@ -65138,7 +65132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32" t="s">
         <v>490</v>
       </c>
@@ -65236,7 +65230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="32" t="s">
         <v>491</v>
       </c>
@@ -65334,7 +65328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="32" t="s">
         <v>492</v>
       </c>
@@ -65432,7 +65426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="32" t="s">
         <v>494</v>
       </c>
@@ -65512,7 +65506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="32" t="s">
         <v>495</v>
       </c>
@@ -65594,7 +65588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A79" s="32" t="s">
         <v>496</v>
       </c>
@@ -65676,7 +65670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="32" t="s">
         <v>497</v>
       </c>
@@ -65758,7 +65752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="32" t="s">
         <v>498</v>
       </c>
@@ -65840,7 +65834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="32" t="s">
         <v>499</v>
       </c>
@@ -65922,7 +65916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="32" t="s">
         <v>500</v>
       </c>
@@ -66004,7 +65998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32" t="s">
         <v>501</v>
       </c>
@@ -66086,7 +66080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="32" t="s">
         <v>502</v>
       </c>
@@ -66168,7 +66162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
         <v>503</v>
       </c>
@@ -66250,7 +66244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="32" t="s">
         <v>504</v>
       </c>
@@ -66332,7 +66326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="32" t="s">
         <v>505</v>
       </c>
@@ -66414,7 +66408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="103" t="s">
         <v>506</v>
       </c>
@@ -66496,7 +66490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
         <v>508</v>
       </c>
@@ -66591,7 +66585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="58" t="s">
         <v>509</v>
       </c>
@@ -66686,7 +66680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="220" t="s">
         <v>510</v>
       </c>
@@ -66824,7 +66818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
         <v>511</v>
       </c>
@@ -66960,7 +66954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A94" s="32" t="s">
         <v>512</v>
       </c>
@@ -67094,7 +67088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="32" t="s">
         <v>513</v>
       </c>
@@ -67225,7 +67219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="32" t="s">
         <v>514</v>
       </c>
@@ -67354,7 +67348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="32" t="s">
         <v>515</v>
       </c>
@@ -67483,7 +67477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="58" t="s">
         <v>516</v>
       </c>
@@ -67612,7 +67606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="78" t="s">
         <v>517</v>
       </c>
@@ -67748,7 +67742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A100" s="32" t="s">
         <v>518</v>
       </c>
@@ -67882,7 +67876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="32" t="s">
         <v>519</v>
       </c>
@@ -68013,7 +68007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="32" t="s">
         <v>520</v>
       </c>
@@ -68149,7 +68143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="32" t="s">
         <v>521</v>
       </c>
@@ -68285,7 +68279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="32" t="s">
         <v>522</v>
       </c>
@@ -68420,7 +68414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="32" t="s">
         <v>523</v>
       </c>
@@ -68556,7 +68550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="32" t="s">
         <v>524</v>
       </c>
@@ -68692,7 +68686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="32" t="s">
         <v>525</v>
       </c>
@@ -68828,7 +68822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="32" t="s">
         <v>526</v>
       </c>
@@ -68964,7 +68958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="32" t="s">
         <v>527</v>
       </c>
@@ -69100,7 +69094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="103" t="s">
         <v>528</v>
       </c>
@@ -69236,7 +69230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A111" s="15" t="s">
         <v>529</v>
       </c>
@@ -69366,7 +69360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="32" t="s">
         <v>530</v>
       </c>
@@ -69490,7 +69484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="103" t="s">
         <v>531</v>
       </c>
@@ -69619,7 +69613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:43" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="15" t="s">
         <v>186</v>
       </c>
@@ -69748,7 +69742,7 @@
       </c>
       <c r="AQ114" s="215"/>
     </row>
-    <row r="115" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="32" t="s">
         <v>532</v>
       </c>
@@ -69878,7 +69872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="32" t="s">
         <v>533</v>
       </c>
@@ -70004,7 +69998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="32" t="s">
         <v>535</v>
       </c>
@@ -70134,7 +70128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="32" t="s">
         <v>536</v>
       </c>
@@ -70259,7 +70253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:43" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="58" t="s">
         <v>538</v>
       </c>
@@ -70386,7 +70380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:43" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A120" s="78" t="s">
         <v>539</v>
       </c>
@@ -70520,7 +70514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="32" t="s">
         <v>540</v>
       </c>
@@ -70652,7 +70646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="32" t="s">
         <v>541</v>
       </c>
@@ -70784,7 +70778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="32" t="s">
         <v>542</v>
       </c>
@@ -70916,7 +70910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="32" t="s">
         <v>543</v>
       </c>
@@ -71048,7 +71042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="32" t="s">
         <v>544</v>
       </c>
@@ -71180,7 +71174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="32" t="s">
         <v>545</v>
       </c>
@@ -71312,7 +71306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="32" t="s">
         <v>546</v>
       </c>
@@ -71437,7 +71431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="32" t="s">
         <v>547</v>
       </c>
@@ -71567,7 +71561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="32" t="s">
         <v>548</v>
       </c>
@@ -71697,7 +71691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="32" t="s">
         <v>549</v>
       </c>
@@ -71827,7 +71821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="32" t="s">
         <v>550</v>
       </c>
@@ -71957,7 +71951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:42" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:42" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="103" t="s">
         <v>551</v>
       </c>
@@ -72087,7 +72081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="188" t="s">
         <v>553</v>
       </c>
@@ -72178,7 +72172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="220" t="s">
         <v>655</v>
       </c>
@@ -72301,7 +72295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:42" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="188" t="s">
         <v>556</v>
       </c>
@@ -72406,7 +72400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:42" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="136" spans="1:42" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -72414,48 +72408,47 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E4374F4-4513-491C-AEC8-03697BD6FF72}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP114"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.73046875" customWidth="1"/>
-    <col min="10" max="11" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="43.265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="80.265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.3984375" style="432" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="37.73046875" customWidth="1"/>
-    <col min="30" max="31" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="432" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="37.7109375" customWidth="1"/>
+    <col min="30" max="31" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="13" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="22.73046875" customWidth="1"/>
-    <col min="37" max="37" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="49.1328125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22.7109375" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:42" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -72583,7 +72576,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>435</v>
       </c>
@@ -72697,7 +72690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
         <v>438</v>
       </c>
@@ -72815,7 +72808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>440</v>
       </c>
@@ -72927,7 +72920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
         <v>442</v>
       </c>
@@ -73039,7 +73032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>437</v>
       </c>
@@ -73159,7 +73152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>433</v>
       </c>
@@ -73289,7 +73282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>436</v>
       </c>
@@ -73420,7 +73413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>434</v>
       </c>
@@ -73551,7 +73544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
         <v>439</v>
       </c>
@@ -73682,7 +73675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="78" t="s">
         <v>441</v>
       </c>
@@ -73813,7 +73806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>446</v>
       </c>
@@ -73946,7 +73939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>186</v>
       </c>
@@ -74075,7 +74068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>533</v>
       </c>
@@ -74202,7 +74195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>536</v>
       </c>
@@ -74328,7 +74321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>538</v>
       </c>
@@ -74456,7 +74449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>57</v>
       </c>
@@ -74586,7 +74579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>447</v>
       </c>
@@ -74710,7 +74703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
         <v>449</v>
       </c>
@@ -74834,7 +74827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
         <v>62</v>
       </c>
@@ -74966,7 +74959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>63</v>
       </c>
@@ -75097,7 +75090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>471</v>
       </c>
@@ -75218,7 +75211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="103" t="s">
         <v>321</v>
       </c>
@@ -75342,7 +75335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>655</v>
       </c>
@@ -75466,7 +75459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>470</v>
       </c>
@@ -75597,7 +75590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
         <v>473</v>
       </c>
@@ -75728,7 +75721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>480</v>
       </c>
@@ -75850,7 +75843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
         <v>444</v>
       </c>
@@ -75973,7 +75966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58" t="s">
         <v>445</v>
       </c>
@@ -76091,7 +76084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="78" t="s">
         <v>476</v>
       </c>
@@ -76219,7 +76212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
         <v>477</v>
       </c>
@@ -76347,7 +76340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>478</v>
       </c>
@@ -76479,7 +76472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
         <v>314</v>
       </c>
@@ -76607,7 +76600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="78" t="s">
         <v>315</v>
       </c>
@@ -76735,7 +76728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="103" t="s">
         <v>518</v>
       </c>
@@ -76866,7 +76859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>519</v>
       </c>
@@ -76994,7 +76987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="32" t="s">
         <v>522</v>
       </c>
@@ -77126,7 +77119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="32" t="s">
         <v>524</v>
       </c>
@@ -77259,7 +77252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78" t="s">
         <v>525</v>
       </c>
@@ -77392,7 +77385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="103" t="s">
         <v>528</v>
       </c>
@@ -77525,7 +77518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>539</v>
       </c>
@@ -77660,7 +77653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="32" t="s">
         <v>540</v>
       </c>
@@ -77793,7 +77786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="32" t="s">
         <v>541</v>
       </c>
@@ -77926,7 +77919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32" t="s">
         <v>542</v>
       </c>
@@ -78059,7 +78052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
         <v>543</v>
       </c>
@@ -78192,7 +78185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
         <v>544</v>
       </c>
@@ -78325,7 +78318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>545</v>
       </c>
@@ -78458,7 +78451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58" t="s">
         <v>546</v>
       </c>
@@ -78584,7 +78577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="78" t="s">
         <v>547</v>
       </c>
@@ -78715,7 +78708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:42" s="289" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:42" s="289" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="433" t="s">
         <v>548</v>
       </c>
@@ -78846,7 +78839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="103" t="s">
         <v>549</v>
       </c>
@@ -78977,7 +78970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="188" t="s">
         <v>550</v>
       </c>
@@ -79108,7 +79101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="78" t="s">
         <v>551</v>
       </c>
@@ -79239,7 +79232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="32" t="s">
         <v>132</v>
       </c>
@@ -79366,7 +79359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="32" t="s">
         <v>134</v>
       </c>
@@ -79494,7 +79487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="32" t="s">
         <v>135</v>
       </c>
@@ -79622,7 +79615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="32" t="s">
         <v>137</v>
       </c>
@@ -79749,7 +79742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="32" t="s">
         <v>138</v>
       </c>
@@ -79877,7 +79870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>140</v>
       </c>
@@ -80005,7 +79998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="32" t="s">
         <v>142</v>
       </c>
@@ -80131,7 +80124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58" t="s">
         <v>143</v>
       </c>
@@ -80259,7 +80252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="78" t="s">
         <v>145</v>
       </c>
@@ -80386,7 +80379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="32" t="s">
         <v>64</v>
       </c>
@@ -80519,7 +80512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="32" t="s">
         <v>451</v>
       </c>
@@ -80652,7 +80645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
         <v>452</v>
       </c>
@@ -80785,7 +80778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="32" t="s">
         <v>453</v>
       </c>
@@ -80916,7 +80909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="32" t="s">
         <v>454</v>
       </c>
@@ -81049,7 +81042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="32" t="s">
         <v>458</v>
       </c>
@@ -81180,7 +81173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32" t="s">
         <v>460</v>
       </c>
@@ -81311,7 +81304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
         <v>461</v>
       </c>
@@ -81439,7 +81432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
         <v>462</v>
       </c>
@@ -81566,7 +81559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="220" t="s">
         <v>463</v>
       </c>
@@ -81693,7 +81686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>468</v>
       </c>
@@ -81826,7 +81819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32" t="s">
         <v>310</v>
       </c>
@@ -81956,7 +81949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="32" t="s">
         <v>313</v>
       </c>
@@ -82084,7 +82077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="32" t="s">
         <v>316</v>
       </c>
@@ -82212,7 +82205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="32" t="s">
         <v>317</v>
       </c>
@@ -82340,7 +82333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="58" t="s">
         <v>481</v>
       </c>
@@ -82458,7 +82451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="78" t="s">
         <v>319</v>
       </c>
@@ -82574,7 +82567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="32" t="s">
         <v>482</v>
       </c>
@@ -82671,7 +82664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="32" t="s">
         <v>483</v>
       </c>
@@ -82766,7 +82759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="32" t="s">
         <v>484</v>
       </c>
@@ -82861,7 +82854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="32" t="s">
         <v>486</v>
       </c>
@@ -82956,7 +82949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="32" t="s">
         <v>487</v>
       </c>
@@ -83051,7 +83044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="32" t="s">
         <v>488</v>
       </c>
@@ -83146,7 +83139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
         <v>489</v>
       </c>
@@ -83241,7 +83234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="32" t="s">
         <v>490</v>
       </c>
@@ -83336,7 +83329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="32" t="s">
         <v>491</v>
       </c>
@@ -83431,7 +83424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="32" t="s">
         <v>492</v>
       </c>
@@ -83526,7 +83519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="103" t="s">
         <v>510</v>
       </c>
@@ -83661,7 +83654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
         <v>511</v>
       </c>
@@ -83794,7 +83787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="32" t="s">
         <v>512</v>
       </c>
@@ -83925,7 +83918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="103" t="s">
         <v>513</v>
       </c>
@@ -84053,7 +84046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
         <v>514</v>
       </c>
@@ -84179,7 +84172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="32" t="s">
         <v>515</v>
       </c>
@@ -84305,7 +84298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="32" t="s">
         <v>516</v>
       </c>
@@ -84431,7 +84424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="32" t="s">
         <v>529</v>
       </c>
@@ -84558,7 +84551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="32" t="s">
         <v>530</v>
       </c>
@@ -84679,7 +84672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="58" t="s">
         <v>531</v>
       </c>
@@ -84805,7 +84798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="78" t="s">
         <v>532</v>
       </c>
@@ -84936,7 +84929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="32" t="s">
         <v>535</v>
       </c>
@@ -85067,7 +85060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="32" t="s">
         <v>465</v>
       </c>
@@ -85185,7 +85178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="32" t="s">
         <v>466</v>
       </c>
@@ -85301,7 +85294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="32" t="s">
         <v>467</v>
       </c>
@@ -85431,7 +85424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="32" t="s">
         <v>469</v>
       </c>
@@ -85559,7 +85552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="32" t="s">
         <v>472</v>
       </c>
@@ -85687,7 +85680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="32" t="s">
         <v>474</v>
       </c>
@@ -85815,7 +85808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="32" t="s">
         <v>517</v>
       </c>
@@ -85948,7 +85941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="32" t="s">
         <v>520</v>
       </c>
@@ -86081,7 +86074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="32" t="s">
         <v>521</v>
       </c>
@@ -86214,7 +86207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="32" t="s">
         <v>523</v>
       </c>
@@ -86347,7 +86340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="103" t="s">
         <v>526</v>
       </c>
@@ -86480,7 +86473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:42" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="220" t="s">
         <v>527</v>
       </c>
@@ -86613,17 +86606,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:42" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
       <c r="AP114" s="215"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP113" xr:uid="{6E4374F4-4513-491C-AEC8-03697BD6FF72}">
-    <filterColumn colId="38">
-      <filters>
-        <filter val="L21_107_05_1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AP113" xr:uid="{6E4374F4-4513-491C-AEC8-03697BD6FF72}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
